--- a/script/data/list.xlsx
+++ b/script/data/list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishel\Desktop\编程总库\MeidiAuto\script\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC90C3D-002F-4278-873E-EC51A9C60919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10171578-E61F-4578-9C3A-6F45802DE987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{B3F25FD5-23CB-4961-973D-5F7EFE73029E}"/>
+    <workbookView xWindow="9540" yWindow="2850" windowWidth="23835" windowHeight="15105" xr2:uid="{B3F25FD5-23CB-4961-973D-5F7EFE73029E}"/>
   </bookViews>
   <sheets>
     <sheet name="2503" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
   <si>
     <t>编号</t>
   </si>
@@ -285,6 +285,30 @@
   </si>
   <si>
     <t>合肥不供</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>比例</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合肥不供，-12.24%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合肥不供30%，-7.38%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合肥不供，1.57%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合肥不供，0.16%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合肥不供，3.05%</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -396,7 +420,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -406,8 +430,11 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -453,8 +480,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 6" xfId="1" xr:uid="{655F6FDC-936D-42A5-A7F3-8B0BF69ECC22}"/>
     <cellStyle name="千位分隔 6" xfId="2" xr:uid="{9466B2A0-24CC-4159-830C-5F1F135E6EA0}"/>
@@ -790,17 +821,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1021F4-B125-4B50-883B-025E82D023CC}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.73046875" style="13" customWidth="1"/>
-    <col min="2" max="2" width="11.86328125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="8"/>
+    <col min="1" max="1" width="15.75" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="10.75" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,8 +847,11 @@
       <c r="E1" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F1" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
@@ -833,8 +867,9 @@
       <c r="E2" s="7" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F2" s="15"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
@@ -850,8 +885,9 @@
       <c r="E3" s="7">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F3" s="15"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>38</v>
       </c>
@@ -862,13 +898,16 @@
         <v>1000</v>
       </c>
       <c r="D4" s="6">
-        <v>2800</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+        <v>5000</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>36</v>
       </c>
@@ -884,8 +923,9 @@
       <c r="E5" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>35</v>
       </c>
@@ -896,13 +936,16 @@
         <v>3000</v>
       </c>
       <c r="D6" s="6">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="E6" s="12">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F6" s="15">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>34</v>
       </c>
@@ -913,13 +956,16 @@
         <v>1000</v>
       </c>
       <c r="D7" s="6">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="E7" s="12">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F7" s="15">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>33</v>
       </c>
@@ -933,8 +979,9 @@
         <v>100</v>
       </c>
       <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>32</v>
       </c>
@@ -950,8 +997,9 @@
       <c r="E9" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>58</v>
       </c>
@@ -965,8 +1013,9 @@
         <v>3000</v>
       </c>
       <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
@@ -980,8 +1029,9 @@
       <c r="E11" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F11" s="15"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>27</v>
       </c>
@@ -992,13 +1042,16 @@
         <v>2000</v>
       </c>
       <c r="D12" s="6">
-        <v>7200</v>
+        <v>3000</v>
       </c>
       <c r="E12" s="12">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F12" s="15">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>18</v>
       </c>
@@ -1010,8 +1063,9 @@
       <c r="E13" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>56</v>
       </c>
@@ -1023,8 +1077,9 @@
       <c r="E14" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>55</v>
       </c>
@@ -1036,8 +1091,9 @@
       <c r="E15" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F15" s="15"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>54</v>
       </c>
@@ -1049,8 +1105,9 @@
       <c r="E16" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F16" s="15"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>53</v>
       </c>
@@ -1066,8 +1123,9 @@
       <c r="E17" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F17" s="15"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>52</v>
       </c>
@@ -1078,11 +1136,16 @@
         <v>1500</v>
       </c>
       <c r="D18" s="6">
-        <v>4500</v>
-      </c>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="F18" s="15">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>51</v>
       </c>
@@ -1098,8 +1161,9 @@
       <c r="E19" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F19" s="15"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
         <v>50</v>
       </c>
@@ -1110,13 +1174,16 @@
         <v>5000</v>
       </c>
       <c r="D20" s="6">
-        <v>15000</v>
+        <v>4000</v>
       </c>
       <c r="E20" s="12">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F20" s="15">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>49</v>
       </c>
@@ -1128,8 +1195,9 @@
       <c r="E21" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F21" s="15"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>48</v>
       </c>
@@ -1140,13 +1208,16 @@
         <v>2000</v>
       </c>
       <c r="D22" s="6">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="E22" s="12">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F22" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>47</v>
       </c>
@@ -1158,8 +1229,9 @@
       <c r="E23" s="7">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F23" s="15"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
         <v>46</v>
       </c>
@@ -1173,14 +1245,17 @@
         <v>16000</v>
       </c>
       <c r="E24" s="12">
-        <v>0.9</v>
+        <v>0.6</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0.6</v>
       </c>
       <c r="G24" s="8">
         <f>18*0.9</f>
         <v>16.2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
         <v>45</v>
       </c>
@@ -1194,8 +1269,9 @@
         <v>1500</v>
       </c>
       <c r="E25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F25" s="15"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>44</v>
       </c>
@@ -1207,8 +1283,9 @@
       <c r="E26" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F26" s="15"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>43</v>
       </c>
@@ -1219,30 +1296,36 @@
         <v>3000</v>
       </c>
       <c r="D27" s="6">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="E27" s="12">
-        <v>0.3</v>
+        <v>0.2</v>
+      </c>
+      <c r="F27" s="15">
+        <v>0.2</v>
       </c>
       <c r="G27" s="8">
         <f>23.4*E27</f>
-        <v>7.02</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>5</v>
+      <c r="B28" s="6">
+        <v>5000</v>
       </c>
       <c r="C28" s="6">
         <v>5000</v>
       </c>
       <c r="D28" s="6">
-        <v>17500</v>
+        <v>30000</v>
       </c>
       <c r="E28" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="F28" s="15">
         <v>0.7</v>
       </c>
       <c r="G28" s="8">
@@ -1250,7 +1333,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
@@ -1262,8 +1345,9 @@
       <c r="E29" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F29" s="15"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
         <v>37</v>
       </c>
@@ -1275,8 +1359,9 @@
       <c r="E30" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F30" s="15"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
         <v>30</v>
       </c>
@@ -1288,8 +1373,9 @@
       <c r="E31" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F31" s="15"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
         <v>29</v>
       </c>
@@ -1301,8 +1387,9 @@
       <c r="E32" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F32" s="15"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
         <v>28</v>
       </c>
@@ -1314,8 +1401,9 @@
       <c r="E33" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F33" s="15"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
         <v>26</v>
       </c>
@@ -1329,10 +1417,11 @@
         <v>0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+      <c r="F34" s="15"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
         <v>25</v>
       </c>
@@ -1344,8 +1433,9 @@
       <c r="E35" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F35" s="15"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
         <v>24</v>
       </c>
@@ -1361,8 +1451,9 @@
       <c r="E36" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
         <v>23</v>
       </c>
@@ -1376,10 +1467,11 @@
         <v>0</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+      <c r="F37" s="15"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>22</v>
       </c>
@@ -1391,8 +1483,9 @@
       <c r="E38" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F38" s="15"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>21</v>
       </c>
@@ -1406,10 +1499,11 @@
         <v>1500</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+      <c r="F39" s="15"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
         <v>20</v>
       </c>
@@ -1425,8 +1519,9 @@
       <c r="E40" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F40" s="15"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
         <v>19</v>
       </c>
@@ -1438,8 +1533,9 @@
       <c r="E41" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F41" s="15"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
         <v>17</v>
       </c>
@@ -1451,8 +1547,9 @@
       <c r="E42" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F42" s="15"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
         <v>16</v>
       </c>
@@ -1468,8 +1565,9 @@
       <c r="E43" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F43" s="15"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
         <v>15</v>
       </c>
@@ -1483,10 +1581,11 @@
         <v>0</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+        <v>67</v>
+      </c>
+      <c r="F44" s="15"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
         <v>14</v>
       </c>
@@ -1497,13 +1596,16 @@
         <v>300</v>
       </c>
       <c r="D45" s="6">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+      <c r="F45" s="15">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
         <v>13</v>
       </c>
@@ -1519,8 +1621,9 @@
       <c r="E46" s="7" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F46" s="15"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
         <v>12</v>
       </c>
@@ -1536,8 +1639,9 @@
       <c r="E47" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F47" s="15"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
         <v>11</v>
       </c>
@@ -1553,8 +1657,9 @@
       <c r="E48" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F48" s="15"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
         <v>10</v>
       </c>
@@ -1570,8 +1675,9 @@
       <c r="E49" s="7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F49" s="15"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
         <v>9</v>
       </c>
@@ -1583,8 +1689,9 @@
       <c r="E50" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F50" s="15"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="10"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -1592,6 +1699,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="7"/>
+      <c r="F51" s="15"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{B64B7257-7777-44DA-82FC-2A7918955D58}">
